--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92571750197</v>
+        <v>46157.93109978824</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93109978824</v>
+        <v>46157.93178534721</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93178534721</v>
+        <v>46157.9340333855</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9340333855</v>
+        <v>46157.93721322111</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93721322111</v>
+        <v>46158.28219329178</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28219329178</v>
+        <v>46158.29694065158</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29694065158</v>
+        <v>46158.2981871192</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2981871192</v>
+        <v>46158.33390390108</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33390390108</v>
+        <v>46158.36860154776</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36860154776</v>
+        <v>46158.37290826161</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
